--- a/artfynd/A 31354-2021 artfynd.xlsx
+++ b/artfynd/A 31354-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119396342</v>
+        <v>119396350</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584602</v>
+        <v>584618</v>
       </c>
       <c r="R2" t="n">
-        <v>7071668</v>
+        <v>7071729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119396348</v>
+        <v>119396345</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119396345</v>
+        <v>119396344</v>
       </c>
       <c r="B4" t="n">
-        <v>79635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>205976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +910,7 @@
         <v>7071742</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119396349</v>
+        <v>119396338</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584618</v>
+        <v>584481</v>
       </c>
       <c r="R5" t="n">
-        <v>7071729</v>
+        <v>7071749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119396350</v>
+        <v>119396339</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584618</v>
+        <v>584477</v>
       </c>
       <c r="R6" t="n">
-        <v>7071729</v>
+        <v>7071749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119396338</v>
+        <v>119396342</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584481</v>
+        <v>584602</v>
       </c>
       <c r="R7" t="n">
-        <v>7071749</v>
+        <v>7071668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119396339</v>
+        <v>119396348</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584477</v>
+        <v>584580</v>
       </c>
       <c r="R8" t="n">
-        <v>7071749</v>
+        <v>7071742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,6 +1351,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119396349</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>584618</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7071729</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
